--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121435245</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R2" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R3" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R2" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R3" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R2" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R3" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R2" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B3" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R3" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R2" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R3" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R2" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R3" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R2" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R3" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54892-2024 artfynd.xlsx
+++ b/artfynd/A 54892-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121435245</v>
+        <v>121435223</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519509</v>
+        <v>519499</v>
       </c>
       <c r="R2" t="n">
-        <v>6995907</v>
+        <v>6995872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121435223</v>
+        <v>121435245</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519499</v>
+        <v>519509</v>
       </c>
       <c r="R3" t="n">
-        <v>6995872</v>
+        <v>6995907</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
